--- a/plantillas/Plantilla_Tareas_Hub_COSMART.xlsx
+++ b/plantillas/Plantilla_Tareas_Hub_COSMART.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tareas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tareas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -450,199 +450,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>PLANTILLA BASE — Carga de tareas al COSMART Marketing Hub</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Esta hoja ('Tareas') tiene una columna por cada campo que reconoce el importador de 'Mis tareas'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Completá una fila por cada tarea.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>CÓMO FUNCIONA LA IMPORTACIÓN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>1. En el hub, sección Mis tareas → botón 'Importar Excel'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2. Subís este archivo (sin cambiar los nombres de las columnas del encabezado, fila 1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>3. Para cada fila, el sistema sugiere un destino (Personal / COSMART interno / un cliente) según lo que</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   pongas en Categoría y Área/Cliente — antes de importar podés revisar y cambiar el destino de cada fila.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>4. Si la tarea ya existe (mismo título en el mismo destino), se avisa y elegís 'Reemplazar' u 'Omitir'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>5. Podés reordenar las columnas — el sistema las identifica por el NOMBRE del encabezado, no por posición.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>6. No borres ni renombres la fila 1 (encabezados). Podés agregar columnas propias al final, se ignoran al subir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CAMPOS OBLIGATORIOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>• Tarea (el título — si esta columna está vacía, se ignora la fila)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>CAMPOS OPCIONALES Y CÓMO SE USAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>• Categoría: escribí "Personal" para que la tarea se sugiera como destino Personal (tuya).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>• Área/Cliente: el nombre del cliente (si coincide con uno ya cargado, se sugiere ese cliente como destino)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  o "Equipo interno" / "Training" / "Capacitación de verticales" para que se sugiera COSMART (interno).</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Si no coincide con nada, queda sin destino sugerido y lo elegís vos a mano antes de importar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>• Prioridad: Alta, Media o Baja (cualquier otro valor, o vacío, se importa como Media).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>• Fecha límite: admite AAAA-MM-DD, DD/MM/AAAA, DD/MM o "15 de septiembre" (usa el año actual si no lo indicás).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>• Día sugerido / Horario / Notas: se combinan en el campo de notas de la tarea, en ese orden.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>Los campos que no están en esta plantilla (subtareas, comentarios, archivos adjuntos, asignación a alguien</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>del equipo, cuadrante Urgente/Importante) se completan después, ya adentro del hub.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -704,7 +511,6 @@
           <t>Personal</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ejemplo: preparar propuesta de campaña</t>
@@ -733,6 +539,199 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>Fila de ejemplo — borrala y cargá tus propias tareas.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="110" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>PLANTILLA BASE — Carga de tareas al COSMART Marketing Hub</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Esta hoja ('Tareas') tiene una columna por cada campo que reconoce el importador de 'Mis tareas'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Completá una fila por cada tarea.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>CÓMO FUNCIONA LA IMPORTACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>1. En el hub, sección Mis tareas → botón 'Importar Excel'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2. Subís este archivo (sin cambiar los nombres de las columnas del encabezado, fila 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>3. Para cada fila, el sistema sugiere un destino (Personal / COSMART interno / un cliente) según lo que</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   pongas en Categoría y Área/Cliente — antes de importar podés revisar y cambiar el destino de cada fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>4. Si la tarea ya existe (mismo título en el mismo destino), se avisa y elegís 'Reemplazar' u 'Omitir'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>5. Podés reordenar las columnas — el sistema las identifica por el NOMBRE del encabezado, no por posición.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>6. No borres ni renombres la fila 1 (encabezados). Podés agregar columnas propias al final, se ignoran al subir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CAMPOS OBLIGATORIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>• Tarea (el título — si esta columna está vacía, se ignora la fila)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>CAMPOS OPCIONALES Y CÓMO SE USAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>• Categoría: escribí "Personal" para que la tarea se sugiera como destino Personal (tuya).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>• Área/Cliente: el nombre del cliente (si coincide con uno ya cargado, se sugiere ese cliente como destino)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  o "Equipo interno" / "Training" / "Capacitación de verticales" para que se sugiera COSMART (interno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Si no coincide con nada, queda sin destino sugerido y lo elegís vos a mano antes de importar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>• Prioridad: Alta, Media o Baja (cualquier otro valor, o vacío, se importa como Media).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>• Fecha límite: admite AAAA-MM-DD, DD/MM/AAAA, DD/MM o "15 de septiembre" (usa el año actual si no lo indicás).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>• Día sugerido / Horario / Notas: se combinan en el campo de notas de la tarea, en ese orden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Los campos que no están en esta plantilla (subtareas, comentarios, archivos adjuntos, asignación a alguien</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>del equipo, cuadrante Urgente/Importante) se completan después, ya adentro del hub.</t>
         </is>
       </c>
     </row>
